--- a/回溯交易记录/持仓明细_2026-05-15.xlsx
+++ b/回溯交易记录/持仓明细_2026-05-15.xlsx
@@ -597,17 +597,17 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>301308</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>电子</t>
+          <t>通信</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="E2" s="4" t="n">
-        <v>479.99</v>
+        <v>331.92</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>1</v>
@@ -625,22 +625,22 @@
         <v>100</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>47999</v>
+        <v>33192</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>590.52</v>
+        <v>399.99</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>59052</v>
+        <v>39999</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>4</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>11053</v>
+        <v>6807</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>23.03</v>
+        <v>20.51</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -656,17 +656,17 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>300394</t>
+          <t>300757</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>罗博特科</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>通信</t>
+          <t>机械设备</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>326.3</v>
+        <v>512.3</v>
       </c>
       <c r="F3" s="7" t="n">
         <v>1</v>
@@ -684,22 +684,22 @@
         <v>100</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>32630</v>
+        <v>51230</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>399.99</v>
+        <v>589.98</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>39999</v>
+        <v>58998</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>4</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>7369</v>
+        <v>7768</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>22.58</v>
+        <v>15.16</v>
       </c>
       <c r="N3" s="6" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>886</v>
+        <v>940.13</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>1</v>
@@ -743,7 +743,7 @@
         <v>100</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>88600</v>
+        <v>94013</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>1049.87</v>
@@ -755,10 +755,10 @@
         <v>4</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>16387</v>
+        <v>10974</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>18.5</v>
+        <v>11.67</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>187.78</v>
+        <v>201.91</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>1</v>
@@ -802,7 +802,7 @@
         <v>100</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>18778</v>
+        <v>20191</v>
       </c>
       <c r="I5" s="7" t="n">
         <v>221.95</v>
@@ -814,10 +814,10 @@
         <v>4</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>3417</v>
+        <v>2004</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>18.2</v>
+        <v>9.93</v>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
@@ -829,17 +829,17 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>002008</t>
+          <t>300502</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>大族激光</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>机械设备</t>
+          <t>通信</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>122.06</v>
+        <v>563.7</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>1</v>
@@ -857,44 +857,48 @@
         <v>100</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>12206</v>
+        <v>56370</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>143.3</v>
+        <v>610.05</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>14330</v>
+        <v>61005</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>4</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>2124</v>
+        <v>4635</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>17.4</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>超2万(最小1手)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>300604</t>
+          <t>002008</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>长川科技</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>电子</t>
+          <t>机械设备</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -903,7 +907,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>182.01</v>
+        <v>134.27</v>
       </c>
       <c r="F7" s="7" t="n">
         <v>1</v>
@@ -912,22 +916,22 @@
         <v>100</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>18201</v>
+        <v>13427</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>209.5</v>
+        <v>143.3</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>20950</v>
+        <v>14330</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>4</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>2749</v>
+        <v>903</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>15.1</v>
+        <v>6.73</v>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
@@ -939,17 +943,17 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>300757</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>罗博特科</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>机械设备</t>
+          <t>电子</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -958,7 +962,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>519.2</v>
+        <v>556.66</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>1</v>
@@ -967,22 +971,22 @@
         <v>100</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>51920</v>
+        <v>55666</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>589.98</v>
+        <v>590.52</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>58998</v>
+        <v>59052</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>4</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>7078</v>
+        <v>3386</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>13.63</v>
+        <v>6.08</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -998,17 +1002,17 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>300502</t>
+          <t>002916</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>深南电路</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>通信</t>
+          <t>电子</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -1017,7 +1021,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>551.67</v>
+        <v>333.52</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>1</v>
@@ -1026,26 +1030,24 @@
         <v>100</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>55167</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>610.05</v>
-      </c>
+        <v>33352</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr"/>
       <c r="J9" s="7" t="n">
-        <v>61005</v>
+        <v>33352</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="L9" s="8" t="n">
-        <v>5838</v>
-      </c>
-      <c r="M9" s="8" t="n">
-        <v>10.58</v>
+      <c r="L9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>无数据</t>
         </is>
       </c>
       <c r="O9" s="6" t="inlineStr">
@@ -1057,17 +1059,17 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>300476</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>胜宏科技</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>通信</t>
+          <t>电子</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1076,7 +1078,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>180.72</v>
+        <v>378.24</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>1</v>
@@ -1085,44 +1087,46 @@
         <v>100</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>18072</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>196.49</v>
-      </c>
+        <v>37824</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="4" t="n">
-        <v>19649</v>
+        <v>37824</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="5" t="n">
-        <v>1577</v>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>8.73</v>
+      <c r="L10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr"/>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>超2万(最小1手)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>688525</t>
+          <t>002080</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>佰维存储</t>
+          <t>中材科技</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>电子</t>
+          <t>建筑材料</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -1131,57 +1135,51 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>290.45</v>
+        <v>63.08</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>29045</v>
-      </c>
-      <c r="I11" s="7" t="n">
-        <v>306.3</v>
-      </c>
+        <v>18924</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr"/>
       <c r="J11" s="7" t="n">
-        <v>30630</v>
+        <v>18924</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="L11" s="8" t="n">
-        <v>1585</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>5.46</v>
+      <c r="L11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="O11" s="6" t="inlineStr">
-        <is>
-          <t>超2万(最小1手)</t>
-        </is>
-      </c>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>600522</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>中天科技</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>通信</t>
+          <t>机械设备</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1190,35 +1188,33 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>40.9</v>
+        <v>102.16</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>16360</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>40.99</v>
-      </c>
+        <v>10216</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="4" t="n">
-        <v>16396</v>
+        <v>10216</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L12" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>0.22</v>
+      <c r="L12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>无数据</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr"/>
@@ -1226,17 +1222,17 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>002080</t>
+          <t>300857</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>中材科技</t>
+          <t>协创数据</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>建筑材料</t>
+          <t>电子</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -1245,20 +1241,20 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>62.4</v>
+        <v>283.94</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>18720</v>
+        <v>28394</v>
       </c>
       <c r="I13" s="6" t="inlineStr"/>
       <c r="J13" s="7" t="n">
-        <v>18720</v>
+        <v>28394</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>4</v>
@@ -1274,22 +1270,26 @@
           <t>无数据</t>
         </is>
       </c>
-      <c r="O13" s="6" t="inlineStr"/>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>超2万(最小1手)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>002281</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>机械设备</t>
+          <t>通信</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>102.28</v>
+        <v>198.79</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>1</v>
@@ -1307,24 +1307,26 @@
         <v>100</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>10228</v>
-      </c>
-      <c r="I14" s="3" t="inlineStr"/>
+        <v>19879</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>196.49</v>
+      </c>
       <c r="J14" s="4" t="n">
-        <v>10228</v>
+        <v>19649</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>0</v>
+      <c r="L14" s="9" t="n">
+        <v>-230</v>
+      </c>
+      <c r="M14" s="9" t="n">
+        <v>-1.16</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>无数据</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr"/>
@@ -1332,17 +1334,17 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>300857</t>
+          <t>301358</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>协创数据</t>
+          <t>湖南裕能</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>电子</t>
+          <t>电力设备</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -1351,50 +1353,48 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>284.5</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>28450</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr"/>
+        <v>19670</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>95.48</v>
+      </c>
       <c r="J15" s="7" t="n">
-        <v>28450</v>
+        <v>19096</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="L15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="7" t="n">
-        <v>0</v>
+      <c r="L15" s="10" t="n">
+        <v>-574</v>
+      </c>
+      <c r="M15" s="10" t="n">
+        <v>-2.92</v>
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>无数据</t>
-        </is>
-      </c>
-      <c r="O15" s="6" t="inlineStr">
-        <is>
-          <t>超2万(最小1手)</t>
-        </is>
-      </c>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>002916</t>
+          <t>688525</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>深南电路</t>
+          <t>佰维存储</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>320.37</v>
+        <v>315.69</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>1</v>
@@ -1417,24 +1417,26 @@
         <v>100</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>32037</v>
-      </c>
-      <c r="I16" s="3" t="inlineStr"/>
+        <v>31569</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>306.3</v>
+      </c>
       <c r="J16" s="4" t="n">
-        <v>32037</v>
+        <v>30630</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="4" t="n">
-        <v>0</v>
+      <c r="L16" s="9" t="n">
+        <v>-939</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <v>-2.97</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>无数据</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -1446,12 +1448,12 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>300476</t>
+          <t>300604</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>胜宏科技</t>
+          <t>长川科技</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -1465,7 +1467,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>358.66</v>
+        <v>218.41</v>
       </c>
       <c r="F17" s="7" t="n">
         <v>1</v>
@@ -1474,46 +1476,44 @@
         <v>100</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>35866</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr"/>
+        <v>21841</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>209.5</v>
+      </c>
       <c r="J17" s="7" t="n">
-        <v>35866</v>
+        <v>20950</v>
       </c>
       <c r="K17" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="L17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="7" t="n">
-        <v>0</v>
+      <c r="L17" s="10" t="n">
+        <v>-891</v>
+      </c>
+      <c r="M17" s="10" t="n">
+        <v>-4.08</v>
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>无数据</t>
-        </is>
-      </c>
-      <c r="O17" s="6" t="inlineStr">
-        <is>
-          <t>超2万(最小1手)</t>
-        </is>
-      </c>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="O17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>300136</t>
+          <t>002353</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>信维通信</t>
+          <t>杰瑞股份</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>电子</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>101.35</v>
+        <v>144.72</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>1</v>
@@ -1531,22 +1531,22 @@
         <v>100</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>10135</v>
+        <v>14472</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>99.61</v>
+        <v>137.86</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>9961</v>
+        <v>13786</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>4</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>-174</v>
+        <v>-686</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>-1.72</v>
+        <v>-4.74</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -1558,17 +1558,17 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>301358</t>
+          <t>601872</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>湖南裕能</t>
+          <t>招商轮船</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>电力设备</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1577,31 +1577,31 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>97.25</v>
+        <v>18.37</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>19450</v>
+        <v>18370</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>95.48</v>
+        <v>17.44</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>19096</v>
+        <v>17440</v>
       </c>
       <c r="K19" s="7" t="n">
         <v>4</v>
       </c>
       <c r="L19" s="10" t="n">
-        <v>-354</v>
+        <v>-930</v>
       </c>
       <c r="M19" s="10" t="n">
-        <v>-1.82</v>
+        <v>-5.06</v>
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
@@ -1613,17 +1613,17 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>300751</t>
+          <t>600673</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>迈为股份</t>
+          <t>东阳光</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>电力设备</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1632,57 +1632,53 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>269.51</v>
+        <v>39.02</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>26951</v>
+        <v>19510</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>260.14</v>
+        <v>36.51</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>26014</v>
+        <v>18255</v>
       </c>
       <c r="K20" s="4" t="n">
         <v>4</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>-937</v>
+        <v>-1255</v>
       </c>
       <c r="M20" s="9" t="n">
-        <v>-3.48</v>
+        <v>-6.43</v>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>超2万(最小1手)</t>
-        </is>
-      </c>
+      <c r="O20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>002384</t>
+          <t>600522</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>中天科技</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>电子</t>
+          <t>通信</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -1691,57 +1687,53 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>211.39</v>
+        <v>43.86</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>21139</v>
+        <v>17544</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>203.35</v>
+        <v>40.99</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>20335</v>
+        <v>16396</v>
       </c>
       <c r="K21" s="7" t="n">
         <v>4</v>
       </c>
       <c r="L21" s="10" t="n">
-        <v>-804</v>
+        <v>-1148</v>
       </c>
       <c r="M21" s="10" t="n">
-        <v>-3.8</v>
+        <v>-6.54</v>
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="O21" s="6" t="inlineStr">
-        <is>
-          <t>超2万(最小1手)</t>
-        </is>
-      </c>
+      <c r="O21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>002353</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>杰瑞股份</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>电子</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1750,7 +1742,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>146.38</v>
+        <v>218.3</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>1</v>
@@ -1759,29 +1751,33 @@
         <v>100</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>14638</v>
+        <v>21830</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>137.86</v>
+        <v>203.35</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>13786</v>
+        <v>20335</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>4</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>-852</v>
+        <v>-1495</v>
       </c>
       <c r="M22" s="9" t="n">
-        <v>-5.82</v>
+        <v>-6.85</v>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr"/>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>超2万(最小1手)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -1805,7 +1801,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>60.47</v>
+        <v>60.64</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>3</v>
@@ -1814,7 +1810,7 @@
         <v>300</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>18141</v>
+        <v>18192</v>
       </c>
       <c r="I23" s="7" t="n">
         <v>56.46</v>
@@ -1826,10 +1822,10 @@
         <v>4</v>
       </c>
       <c r="L23" s="10" t="n">
-        <v>-1203</v>
+        <v>-1254</v>
       </c>
       <c r="M23" s="10" t="n">
-        <v>-6.63</v>
+        <v>-6.89</v>
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
@@ -1841,17 +1837,17 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>688702</t>
+          <t>600487</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>盛科通信</t>
+          <t>亨通光电</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>通信</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1860,57 +1856,53 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>307.88</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>30788</v>
+        <v>14998</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>285</v>
+        <v>69.8</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>28500</v>
+        <v>13960</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>4</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>-2288</v>
+        <v>-1038</v>
       </c>
       <c r="M24" s="9" t="n">
-        <v>-7.43</v>
+        <v>-6.92</v>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>超2万(最小1手)</t>
-        </is>
-      </c>
+      <c r="O24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>600673</t>
+          <t>300751</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>东阳光</t>
+          <t>迈为股份</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电力设备</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1919,53 +1911,57 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>39.9</v>
+        <v>285.88</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>19950</v>
+        <v>28588</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>36.51</v>
+        <v>260.14</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>18255</v>
+        <v>26014</v>
       </c>
       <c r="K25" s="7" t="n">
         <v>4</v>
       </c>
       <c r="L25" s="10" t="n">
-        <v>-1695</v>
+        <v>-2574</v>
       </c>
       <c r="M25" s="10" t="n">
-        <v>-8.5</v>
+        <v>-9</v>
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="O25" s="6" t="inlineStr"/>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>超2万(最小1手)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>688387</t>
+          <t>600176</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>信科移动</t>
+          <t>中国巨石</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>通信</t>
+          <t>建筑材料</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -1974,31 +1970,31 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>21.77</v>
+        <v>38.01</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>19593</v>
+        <v>19005</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>19.81</v>
+        <v>33.86</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>17829</v>
+        <v>16930</v>
       </c>
       <c r="K26" s="4" t="n">
         <v>4</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>-1764</v>
+        <v>-2075</v>
       </c>
       <c r="M26" s="9" t="n">
-        <v>-9</v>
+        <v>-10.92</v>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
@@ -2010,17 +2006,17 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>300390</t>
+          <t>688702</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>天华新能</t>
+          <t>盛科通信</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>电力设备</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -2029,7 +2025,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>103.45</v>
+        <v>320.02</v>
       </c>
       <c r="F27" s="7" t="n">
         <v>1</v>
@@ -2038,44 +2034,48 @@
         <v>100</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>10345</v>
+        <v>32002</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>93.65000000000001</v>
+        <v>285</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>9365</v>
+        <v>28500</v>
       </c>
       <c r="K27" s="7" t="n">
         <v>4</v>
       </c>
       <c r="L27" s="10" t="n">
-        <v>-980</v>
+        <v>-3502</v>
       </c>
       <c r="M27" s="10" t="n">
-        <v>-9.470000000000001</v>
+        <v>-10.94</v>
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="O27" s="6" t="inlineStr"/>
+      <c r="O27" s="6" t="inlineStr">
+        <is>
+          <t>超2万(最小1手)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>600487</t>
+          <t>300390</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>天华新能</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>通信</t>
+          <t>电力设备</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -2084,31 +2084,31 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>77.27</v>
+        <v>105.5</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>15454</v>
+        <v>10550</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>69.8</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>13960</v>
+        <v>9365</v>
       </c>
       <c r="K28" s="4" t="n">
         <v>4</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>-1494</v>
+        <v>-1185</v>
       </c>
       <c r="M28" s="9" t="n">
-        <v>-9.67</v>
+        <v>-11.23</v>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
@@ -2120,17 +2120,17 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>601872</t>
+          <t>688387</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>招商轮船</t>
+          <t>信科移动</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>通信</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -2139,31 +2139,31 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>19.49</v>
+        <v>22.45</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>19490</v>
+        <v>20205</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>17.44</v>
+        <v>19.81</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>17440</v>
+        <v>17829</v>
       </c>
       <c r="K29" s="7" t="n">
         <v>4</v>
       </c>
       <c r="L29" s="10" t="n">
-        <v>-2050</v>
+        <v>-2376</v>
       </c>
       <c r="M29" s="10" t="n">
-        <v>-10.52</v>
+        <v>-11.76</v>
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
@@ -2175,17 +2175,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>600176</t>
+          <t>300136</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>中国巨石</t>
+          <t>信维通信</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>建筑材料</t>
+          <t>电子</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -2194,31 +2194,31 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>38</v>
+        <v>115.57</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>19000</v>
+        <v>11557</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>33.86</v>
+        <v>99.61</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>16930</v>
+        <v>9961</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>4</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>-2070</v>
+        <v>-1596</v>
       </c>
       <c r="M30" s="9" t="n">
-        <v>-10.89</v>
+        <v>-13.81</v>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>114.18</v>
+        <v>116.11</v>
       </c>
       <c r="F31" s="7" t="n">
         <v>1</v>
@@ -2258,7 +2258,7 @@
         <v>100</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>11418</v>
+        <v>11611</v>
       </c>
       <c r="I31" s="7" t="n">
         <v>95.81999999999999</v>
@@ -2270,10 +2270,10 @@
         <v>4</v>
       </c>
       <c r="L31" s="10" t="n">
-        <v>-1836</v>
+        <v>-2029</v>
       </c>
       <c r="M31" s="10" t="n">
-        <v>-16.08</v>
+        <v>-17.47</v>
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
@@ -2299,20 +2299,20 @@
         <v>6400</v>
       </c>
       <c r="H32" s="11" t="n">
-        <v>770771</v>
+        <v>804192</v>
       </c>
       <c r="I32" s="11" t="inlineStr"/>
       <c r="J32" s="11" t="n">
-        <v>811483</v>
+        <v>814892</v>
       </c>
       <c r="K32" s="11" t="n">
         <v>4</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>40712</v>
+        <v>10700</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>5.28</v>
+        <v>1.33</v>
       </c>
       <c r="N32" s="11" t="inlineStr">
         <is>
